--- a/reports/pdf_weekly_20260918.xlsx
+++ b/reports/pdf_weekly_20260918.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 57억(1.2%)      주말 2026-09-18  vs  주초 2026-09-14      매수 10종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 29억(0.6%)      주말 2026-09-18  vs  주초 2026-09-14      매수 10종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1316615958</v>
+        <v>2172171085</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.81%</t>
+          <t>0.79%→1.22%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2172171085</v>
+        <v>1316615958</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.79%→1.22%</t>
+          <t>1.56%→1.81%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오  (편출)</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-528528264</v>
+        <v>-294374227</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.00%</t>
+          <t>0.23%→0.15%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>16→0</t>
+          <t>53→37</t>
         </is>
       </c>
     </row>
@@ -1103,23 +1103,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>지투지바이오  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-294374227</v>
+        <v>-528528264</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.15%</t>
+          <t>0.12%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>53→37</t>
+          <t>16→0</t>
         </is>
       </c>
     </row>
@@ -1215,23 +1215,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-835334917</v>
+        <v>-1243743121</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.93%</t>
+          <t>3.07%→2.61%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1243743121</v>
+        <v>-835334917</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.61%</t>
+          <t>6.81%→6.93%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 118억(3.4%)      주말 2026-09-18  vs  주초 2026-09-14      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 59억(1.7%)      주말 2026-09-18  vs  주초 2026-09-14      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1411,7 +1411,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 76억(2.9%)      주말 2026-09-18  vs  주초 2026-09-14      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 38억(1.5%)      주말 2026-09-18  vs  주초 2026-09-14      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1609,23 +1609,23 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-475695014</v>
+        <v>-2086920061</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.44%</t>
+          <t>5.98%→4.99%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>50→35</t>
+          <t>105→90</t>
         </is>
       </c>
     </row>
@@ -1637,30 +1637,30 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2086920061</v>
+        <v>-475695014</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>5.98%→4.99%</t>
+          <t>0.65%→0.44%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>105→90</t>
+          <t>50→35</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 26억(1.3%)      주말 2026-09-18  vs  주초 2026-09-14      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 13억(0.7%)      주말 2026-09-18  vs  주초 2026-09-14      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1925,7 +1925,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 3억(1.2%)      주말 2026-09-18  vs  주초 2026-09-14      매수 7종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 2억(0.6%)      주말 2026-09-18  vs  주초 2026-09-14      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2274,7 +2274,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 486억   ·   현금 5억(1.1%)      주말 2026-09-18  vs  주초 2026-09-14      매수 3종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 486억   ·   현금 3억(0.6%)      주말 2026-09-18  vs  주초 2026-09-14      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>

--- a/reports/pdf_weekly_20260918.xlsx
+++ b/reports/pdf_weekly_20260918.xlsx
@@ -1215,23 +1215,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1243743121</v>
+        <v>-835334917</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.61%</t>
+          <t>6.81%→6.93%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-835334917</v>
+        <v>-1243743121</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.93%</t>
+          <t>3.07%→2.61%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260918.xlsx
+++ b/reports/pdf_weekly_20260918.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2172171085</v>
+        <v>1316615958</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.79%→1.22%</t>
+          <t>1.56%→1.81%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1316615958</v>
+        <v>2172171085</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.81%</t>
+          <t>0.79%→1.22%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>지투지바이오  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-294374227</v>
+        <v>-528528264</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.15%</t>
+          <t>0.12%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>53→37</t>
+          <t>16→0</t>
         </is>
       </c>
     </row>
@@ -1103,23 +1103,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오  (편출)</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-528528264</v>
+        <v>-294374227</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.00%</t>
+          <t>0.23%→0.15%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>16→0</t>
+          <t>53→37</t>
         </is>
       </c>
     </row>
@@ -1215,23 +1215,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-835334917</v>
+        <v>-1243743121</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.93%</t>
+          <t>3.07%→2.61%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1243743121</v>
+        <v>-835334917</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.61%</t>
+          <t>6.81%→6.93%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>
@@ -1609,23 +1609,23 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2086920061</v>
+        <v>-475695014</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>5.98%→4.99%</t>
+          <t>0.65%→0.44%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>105→90</t>
+          <t>50→35</t>
         </is>
       </c>
     </row>
@@ -1637,23 +1637,23 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-475695014</v>
+        <v>-2086920061</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.44%</t>
+          <t>5.98%→4.99%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>50→35</t>
+          <t>105→90</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260918.xlsx
+++ b/reports/pdf_weekly_20260918.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1316615958</v>
+        <v>2172171085</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.81%</t>
+          <t>0.79%→1.22%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2172171085</v>
+        <v>1316615958</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.79%→1.22%</t>
+          <t>1.56%→1.81%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1215,23 +1215,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1243743121</v>
+        <v>-835334917</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.61%</t>
+          <t>6.81%→6.93%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-835334917</v>
+        <v>-1243743121</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.93%</t>
+          <t>3.07%→2.61%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>
